--- a/Documentation/pathologies.xlsx
+++ b/Documentation/pathologies.xlsx
@@ -1,52 +1,295 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="Calc"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2">
+  <fileVersion appName="Calc" lowestEdited="4"/>
   <workbookPr backupFile="false" showObjects="all" date1904="false"/>
   <workbookProtection/>
   <bookViews>
     <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="0"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId2"/>
+    <sheet name="Feuil1" sheetId="1" state="visible" r:id="rId3"/>
   </sheets>
-  <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.001"/>
+  <definedNames>
+    <definedName function="false" hidden="true" localSheetId="0" name="_xlnm._FilterDatabase" vbProcedure="false">Feuil1!$A$1:$E$47</definedName>
+  </definedNames>
+  <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.0001"/>
   <extLst>
     <ext xmlns:loext="http://schemas.libreoffice.org/" uri="{7626C862-2A13-11E5-B345-FEFF819CDC9F}">
-      <loext:extCalcPr stringRefSyntax="CalcA1"/>
+      <loext:extCalcPr stringRefSyntax="CalcA1ExcelA1"/>
     </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9" uniqueCount="9">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="135" uniqueCount="89">
+  <si>
+    <t xml:space="preserve">Pathology/phenotype/cohort name</t>
+  </si>
   <si>
     <t xml:space="preserve">pathologyID</t>
   </si>
   <si>
+    <t xml:space="preserve">no_files</t>
+  </si>
+  <si>
+    <t xml:space="preserve">is_a</t>
+  </si>
+  <si>
     <t xml:space="preserve">compatibility groups</t>
   </si>
   <si>
+    <t xml:space="preserve">Female infertility</t>
+  </si>
+  <si>
+    <t xml:space="preserve">INF_F</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Oocytes Maturation Deficiency</t>
+  </si>
+  <si>
+    <t xml:space="preserve">OMD</t>
+  </si>
+  <si>
+    <t xml:space="preserve">G1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Premature Ovarian Failure</t>
+  </si>
+  <si>
+    <t xml:space="preserve">POF</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Endometriosis</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ENDO</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Polycystic Ovarian Syndrome</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PCOS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Female functional defects</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FUNC_F</t>
+  </si>
+  <si>
+    <t xml:space="preserve">G2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Male infertility</t>
+  </si>
+  <si>
+    <t xml:space="preserve">INF_M</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Quantitative sperm defects</t>
+  </si>
+  <si>
+    <t xml:space="preserve">QUANT</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Qualitative sperm defects</t>
+  </si>
+  <si>
+    <t xml:space="preserve">QUAL</t>
+  </si>
+  <si>
+    <t xml:space="preserve">G3,G4</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Male functional defects</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FUNC_M</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fertilization failure, female</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FF_F</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Arrest of preimplantation development, female</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PreImpA_F</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Recurrent pregrnancy loss, female</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RPL_F</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fertilization failure, male</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FF_M</t>
+  </si>
+  <si>
+    <t xml:space="preserve">G2,G4</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Arrest of preimplantation development, male</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PreImpA_M</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Recurrent pregrnancy loss, male</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RPL_M</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mild Oligozoospermia (&gt;10M/ml ; &lt;20M/ml)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">OL_MILD</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Moderate Oligozoospermia (&gt;5M/ml ; &lt;10M/ml)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">OL_MOD</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Severe oligozoospermia (&gt;1M/ml ; &lt;5M/ml)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">OL_SEVERE</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Extreme oligozoospermia (&lt;1M/ml)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">OL_EXTREME</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Azoospermia</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AZOO</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Obstructive Azoospermia</t>
+  </si>
+  <si>
+    <t xml:space="preserve">OA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Non-Obstructive Azoospermia</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NOA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sperm motility defect</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MOTIL</t>
+  </si>
+  <si>
+    <t xml:space="preserve">G3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sperm morphological defect</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MORPHO</t>
+  </si>
+  <si>
+    <t xml:space="preserve">G4</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Asthenozoospermia, Akinetozoospermia</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AST</t>
+  </si>
+  <si>
     <t xml:space="preserve">MMAF</t>
   </si>
   <si>
-    <t xml:space="preserve">C1,C2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ovo</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AST</t>
-  </si>
-  <si>
-    <t xml:space="preserve">C1</t>
+    <t xml:space="preserve">MOTIL,MORPHO</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Macrospermia</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Macro</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MORPHO,QUANT</t>
+  </si>
+  <si>
+    <t xml:space="preserve">G1,G4</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Globozoospermia</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Globo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MORPHO,FF_M</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Headless spermatozooa</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Headless</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MORPHO,MOTIL</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Oligo-Astheno-teratozoospermia</t>
+  </si>
+  <si>
+    <t xml:space="preserve">OAT</t>
+  </si>
+  <si>
+    <t xml:space="preserve">QUANT,MOTIL,MORPHO</t>
+  </si>
+  <si>
+    <t xml:space="preserve">G1,G3,G4</t>
+  </si>
+  <si>
+    <t xml:space="preserve">maleInf Muenster, various morph/motility defects</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MorphMot</t>
+  </si>
+  <si>
+    <t xml:space="preserve">G2,G3,G4</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Disorders of sexual development </t>
+  </si>
+  <si>
+    <t xml:space="preserve">DSD</t>
+  </si>
+  <si>
+    <t xml:space="preserve">INF_F,INF_M</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Primary ciliary dyskinesia</t>
   </si>
   <si>
     <t xml:space="preserve">PCD</t>
   </si>
   <si>
-    <t xml:space="preserve">C2</t>
+    <t xml:space="preserve">Fertile controls</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FERTILE</t>
   </si>
 </sst>
 </file>
@@ -56,11 +299,12 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="General"/>
   </numFmts>
-  <fonts count="5">
+  <fonts count="4">
     <font>
-      <sz val="10"/>
-      <name val="Arial"/>
-      <family val="2"/>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
+      <family val="0"/>
       <charset val="1"/>
     </font>
     <font>
@@ -77,13 +321,6 @@
       <sz val="10"/>
       <name val="Arial"/>
       <family val="0"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF000000"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <charset val="1"/>
     </font>
   </fonts>
   <fills count="3">
@@ -134,12 +371,24 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="5">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="2" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -152,6 +401,31 @@
     <cellStyle name="Currency [0]" xfId="18" builtinId="7"/>
     <cellStyle name="Percent" xfId="19" builtinId="5"/>
   </cellStyles>
+  <dxfs count="3">
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFF2F2F2"/>
+          <bgColor rgb="FF000000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FF000000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF000000"/>
+          <bgColor rgb="FF000000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+  </dxfs>
   <colors>
     <indexedColors>
       <rgbColor rgb="FF000000"/>
@@ -215,62 +489,701 @@
 </styleSheet>
 </file>
 
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships"/>
+</file>
+
+<file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Thème Office">
+  <a:themeElements>
+    <a:clrScheme name="Office">
+      <a:dk1>
+        <a:srgbClr val="000000"/>
+      </a:dk1>
+      <a:lt1>
+        <a:srgbClr val="FFFFFF"/>
+      </a:lt1>
+      <a:dk2>
+        <a:srgbClr val="44546A"/>
+      </a:dk2>
+      <a:lt2>
+        <a:srgbClr val="E7E6E6"/>
+      </a:lt2>
+      <a:accent1>
+        <a:srgbClr val="4472C4"/>
+      </a:accent1>
+      <a:accent2>
+        <a:srgbClr val="ED7D31"/>
+      </a:accent2>
+      <a:accent3>
+        <a:srgbClr val="A5A5A5"/>
+      </a:accent3>
+      <a:accent4>
+        <a:srgbClr val="FFC000"/>
+      </a:accent4>
+      <a:accent5>
+        <a:srgbClr val="5B9BD5"/>
+      </a:accent5>
+      <a:accent6>
+        <a:srgbClr val="70AD47"/>
+      </a:accent6>
+      <a:hlink>
+        <a:srgbClr val="0563C1"/>
+      </a:hlink>
+      <a:folHlink>
+        <a:srgbClr val="954F72"/>
+      </a:folHlink>
+    </a:clrScheme>
+    <a:fontScheme name="Office">
+      <a:majorFont>
+        <a:latin typeface="Calibri Light" pitchFamily="0" charset="1"/>
+        <a:ea typeface="Arial" pitchFamily="0" charset="1"/>
+        <a:cs typeface="Arial" pitchFamily="0" charset="1"/>
+      </a:majorFont>
+      <a:minorFont>
+        <a:latin typeface="Calibri" pitchFamily="0" charset="1"/>
+        <a:ea typeface="Arial" pitchFamily="0" charset="1"/>
+        <a:cs typeface="Arial" pitchFamily="0" charset="1"/>
+      </a:minorFont>
+    </a:fontScheme>
+    <a:fmtScheme>
+      <a:fillStyleLst>
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:gradFill>
+          <a:gsLst>
+            <a:gs pos="0">
+              <a:schemeClr val="phClr">
+                <a:lumMod val="110000"/>
+                <a:tint val="67000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="50000">
+              <a:schemeClr val="phClr">
+                <a:lumMod val="105000"/>
+                <a:tint val="73000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="100000">
+              <a:schemeClr val="phClr">
+                <a:lumMod val="105000"/>
+                <a:tint val="81000"/>
+              </a:schemeClr>
+            </a:gs>
+          </a:gsLst>
+          <a:lin ang="5400000" scaled="0"/>
+          <a:tileRect l="0" t="0" r="0" b="0"/>
+        </a:gradFill>
+        <a:gradFill>
+          <a:gsLst>
+            <a:gs pos="0">
+              <a:schemeClr val="phClr">
+                <a:lumMod val="102000"/>
+                <a:tint val="94000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="50000">
+              <a:schemeClr val="phClr">
+                <a:lumMod val="100000"/>
+                <a:shade val="100000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="100000">
+              <a:schemeClr val="phClr">
+                <a:lumMod val="99000"/>
+                <a:shade val="78000"/>
+              </a:schemeClr>
+            </a:gs>
+          </a:gsLst>
+          <a:lin ang="5400000" scaled="0"/>
+          <a:tileRect l="0" t="0" r="0" b="0"/>
+        </a:gradFill>
+      </a:fillStyleLst>
+      <a:lnStyleLst>
+        <a:ln w="6350" cap="flat" cmpd="sng" algn="ctr">
+          <a:prstDash val="solid"/>
+          <a:miter lim="800000"/>
+        </a:ln>
+        <a:ln w="12700" cap="flat" cmpd="sng" algn="ctr">
+          <a:prstDash val="solid"/>
+          <a:miter lim="800000"/>
+        </a:ln>
+        <a:ln w="19050" cap="flat" cmpd="sng" algn="ctr">
+          <a:prstDash val="solid"/>
+          <a:miter lim="800000"/>
+        </a:ln>
+      </a:lnStyleLst>
+      <a:effectStyleLst>
+        <a:effectStyle>
+          <a:effectLst/>
+        </a:effectStyle>
+        <a:effectStyle>
+          <a:effectLst/>
+        </a:effectStyle>
+        <a:effectStyle>
+          <a:effectLst/>
+        </a:effectStyle>
+      </a:effectStyleLst>
+      <a:bgFillStyleLst>
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:solidFill>
+          <a:schemeClr val="phClr">
+            <a:tint val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:gradFill>
+          <a:gsLst>
+            <a:gs pos="0">
+              <a:schemeClr val="phClr">
+                <a:tint val="93000"/>
+                <a:shade val="98000"/>
+                <a:lumMod val="102000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="50000">
+              <a:schemeClr val="phClr">
+                <a:tint val="98000"/>
+                <a:shade val="90000"/>
+                <a:lumMod val="103000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="100000">
+              <a:schemeClr val="phClr">
+                <a:shade val="63000"/>
+              </a:schemeClr>
+            </a:gs>
+          </a:gsLst>
+          <a:lin ang="5400000" scaled="0"/>
+          <a:tileRect l="0" t="0" r="0" b="0"/>
+        </a:gradFill>
+      </a:bgFillStyleLst>
+    </a:fmtScheme>
+  </a:themeElements>
+</a:theme>
+</file>
+
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:B5"/>
-  <sheetFormatPr defaultColWidth="11.5703125" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <dimension ref="A1:AMN47"/>
+  <sheetFormatPr defaultColWidth="11.54296875" defaultRowHeight="14.25" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="12.13"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="19.21"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="46"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="14.27"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="18.18"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="15.18"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="18.45"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1023" min="6" style="1" width="9.45"/>
+    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="1025" min="1024" style="1" width="11.54"/>
+    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="16381" min="1029" style="1" width="11.54"/>
+    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="16384" min="16382" style="1" width="11.53"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="1" t="s">
+    <row r="1" s="4" customFormat="true" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" s="2" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="0" t="s">
+      <c r="C1" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="B2" s="0" t="s">
+      <c r="D1" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="0" t="s">
+      <c r="E1" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="0" t="s">
+      <c r="AMJ1" s="1"/>
+      <c r="AMK1" s="1"/>
+      <c r="AML1" s="0"/>
+      <c r="AMM1" s="0"/>
+      <c r="AMN1" s="0"/>
+    </row>
+    <row r="3" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A3" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="B4" s="0" t="s">
+      <c r="B3" s="1" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="0" t="s">
+    <row r="4" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A4" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="B5" s="0" t="s">
+      <c r="B4" s="1" t="s">
         <v>8</v>
       </c>
+      <c r="D4" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="E4" s="1" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="5" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A5" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="D5" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="E5" s="1" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="6" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A6" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="D6" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="7" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A7" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="B7" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="D7" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="8" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A8" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="B8" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="D8" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="E8" s="1" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="10" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A10" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="B10" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="C10" s="1" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="11" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A11" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="B11" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="D11" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="E11" s="1" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="12" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A12" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="B12" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="C12" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="D12" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="E12" s="1" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="13" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A13" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="B13" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="D13" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="E13" s="1" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="15" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A15" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="B15" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="D15" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="E15" s="1" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="16" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A16" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="B16" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="D16" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="E16" s="1" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="17" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A17" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="B17" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="D17" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="E17" s="1" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="19" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A19" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="B19" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="D19" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="E19" s="1" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="20" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A20" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="B20" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="D20" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="E20" s="1" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="21" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A21" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="B21" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="D21" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="E21" s="1" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="23" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A23" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="B23" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="D23" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="E23" s="1" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="24" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A24" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="B24" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="D24" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="E24" s="1" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="25" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A25" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="B25" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="D25" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="E25" s="1" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="26" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A26" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="B26" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="D26" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="E26" s="1" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="27" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A27" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="B27" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="C27" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="D27" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="E27" s="1" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="28" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A28" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="B28" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="D28" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="E28" s="1" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="29" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A29" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="B29" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="D29" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="E29" s="1" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="31" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A31" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="B31" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="D31" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="E31" s="1" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="32" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A32" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="B32" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="D32" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="E32" s="1" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="33" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A33" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="B33" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="D33" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="E33" s="1" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="34" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A34" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="B34" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="D34" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="E34" s="1" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="35" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A35" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="B35" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="D35" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="E35" s="1" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="36" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A36" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="B36" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="D36" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="E36" s="1" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="37" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A37" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="B37" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="D37" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="E37" s="1" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="39" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A39" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="B39" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="D39" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="E39" s="1" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="41" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A41" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="B41" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="D41" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="E41" s="1" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="43" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A43" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="B43" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="D43" s="1" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="45" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A45" s="1" t="s">
+        <v>85</v>
+      </c>
+      <c r="B45" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="E45" s="1" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="47" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A47" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="B47" s="1" t="s">
+        <v>88</v>
+      </c>
     </row>
   </sheetData>
+  <autoFilter ref="A1:E47"/>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
-  <pageMargins left="0.7875" right="0.7875" top="1.05277777777778" bottom="1.05277777777778" header="0.7875" footer="0.7875"/>
-  <pageSetup paperSize="1" scale="100" firstPageNumber="1" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" useFirstPageNumber="true" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511811023622047" footer="0.511811023622047"/>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
   <headerFooter differentFirst="false" differentOddEven="false">
-    <oddHeader>&amp;C&amp;"Times New Roman,Regular"&amp;12&amp;A</oddHeader>
-    <oddFooter>&amp;C&amp;"Times New Roman,Regular"&amp;12Page &amp;P</oddFooter>
+    <oddHeader/>
+    <oddFooter/>
   </headerFooter>
+  <drawing r:id="rId1"/>
 </worksheet>
 </file>